--- a/processed_ruby_restored_xlsx/sc224_瑠璃６：おしりペンペン.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc224_瑠璃６：おしりペンペン.ss.xlsx
@@ -500,8 +500,8 @@
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Having spent the whole morning cleaning the dorm,
-finished lunch, and for a moment to unwind, I was just
-chilling in the living room.</t>
+finished lunch, and for a moment to unwind, I was
+just chilling in the living room.</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -745,8 +745,8 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>And that's Rurichiyo-chan's panties that I happened to
-pick up the other day and was keeping in my room.</t>
+          <t>And that's Rurichiyo-chan's panties that I happened
+to pick up the other day and was keeping in my room.</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -942,8 +942,9 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Although I never skipped cleaning the dorm, at heart I
-was lazy, and I found cleaning my own room bothersome.</t>
+          <t>Although I never skipped cleaning the dorm, at heart
+I was lazy, and I found cleaning my own room
+bothersome.</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1020,8 +1021,8 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>『That's it — as thanks for always keeping things tidy,
-I'll clean Oji-sama's room for you！』</t>
+          <t>『That's it — as thanks for always keeping things
+tidy, I'll clean Oji-sama's room for you！』</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1361,8 +1362,9 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>Maybe Rurichiyo-chan was conscious of the others being
-around too; she said that and started walking ahead.</t>
+          <t>Maybe Rurichiyo-chan was conscious of the others
+being around too; she said that and started walking
+ahead.</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1824,8 +1826,9 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>Or maybe it's jealousy, but with the physical evidence
-in hand this time, there's no way to make any excuses.</t>
+          <t>Or maybe it's jealousy, but with the physical
+evidence in hand this time, there's no way to make
+any excuses.</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1931,7 +1934,8 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>...Turns out it was just a setup for an interrogation.</t>
+          <t>...Turns out it was just a setup for an
+interrogation.</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2177,8 +2181,8 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan doesn't raise her voice, but there's an
-unmistakable, no-arguments-allowed vibe about her.</t>
+          <t>Rurichiyo-chan doesn't raise her voice, but there's
+an unmistakable, no-arguments-allowed vibe about her.</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2301,8 +2305,8 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>My crotch felt cool and I couldn't help but notice it,
-but this time the penis was really unnecessary...</t>
+          <t>My crotch felt cool and I couldn't help but notice
+it, but this time the penis was really unnecessary...</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2901,8 +2905,8 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama... hey, you're looking elsewhere！ You're not
-even sorry, are you！？」</t>
+          <t>「Oji-sama... hey, you're looking elsewhere！ You're
+not even sorry, are you！？」</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -3098,8 +3102,8 @@
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>I calmed at the feeling of my butt being struck, yet I
-apologized earnestly.</t>
+          <t>I calmed at the feeling of my butt being struck, yet
+I apologized earnestly.</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3435,7 +3439,8 @@
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>「So you really haven't reflected on this, have you...」</t>
+          <t>「So you really haven't reflected on this, have
+you...」</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3496,8 +3501,8 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>「Honestly…you've made it so big…why can't you properly
-say 'penis'？」</t>
+          <t>「Honestly…you've made it so big…why can't you
+properly say 'penis'？」</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3634,7 +3639,8 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>「Nn, ahem！ ...So, why did you make your penis bigger？」</t>
+          <t>「Nn, ahem！ ...So, why did you make your penis
+bigger？」</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3698,8 +3704,8 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>Already worked up from a maternal spanking, I ended up
-wanting to be coddled.</t>
+          <t>Already worked up from a maternal spanking, I ended
+up wanting to be coddled.</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -4365,8 +4371,8 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>「This is... turning into something we really shouldn’t
-be doing...」</t>
+          <t>「This is... turning into something we really
+shouldn’t be doing...」</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4428,7 +4434,8 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>「Ahaha... then wouldn’t that stop being a punishment？」</t>
+          <t>「Ahaha... then wouldn’t that stop being a
+punishment？」</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -5249,8 +5256,8 @@
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t>…In time with that sound, the penis grew more and more
-excited.</t>
+          <t>…In time with that sound, the penis grew more and
+more excited.</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5387,7 +5394,8 @@
       </c>
       <c r="B320" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan turned her attention back to the penis.</t>
+          <t>Rurichiyo-chan turned her attention back to the
+penis.</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5493,8 +5501,8 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>My charged-up penis wobbled around in Rurichiyo-chan's
-hand.</t>
+          <t>My charged-up penis wobbled around in
+Rurichiyo-chan's hand.</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -5586,8 +5594,8 @@
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t>I don't want to be stopped, so I fake a laugh and just
-go along with how things are.</t>
+          <t>I don't want to be stopped, so I fake a laugh and
+just go along with how things are.</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -5632,8 +5640,9 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo-chan suddenly dropped her face down and this
-time lightly took the tip into her mouth and sucked.</t>
+          <t>Rurichiyo-chan suddenly dropped her face down and
+this time lightly took the tip into her mouth and
+sucked.</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -6030,8 +6039,8 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>Feeling the warmth of Rurichiyo-chan's mouth, my penis
-instantly regained its vigor.</t>
+          <t>Feeling the warmth of Rurichiyo-chan's mouth, my
+penis instantly regained its vigor.</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -6076,8 +6085,9 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t>…Because of my way-too-practical penis, Rurichiyo-chan
-was exasperated with me and scolded me.</t>
+          <t>…Because of my way-too-practical penis,
+Rurichiyo-chan was exasperated with me and scolded
+me.</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -6154,8 +6164,8 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>「smack… chu, chuu, chut, chu！ slurp slurp… nfuuh, nff,
-fuu…！」</t>
+          <t>「smack… chu, chuu, chut, chu！ slurp slurp… nfuuh,
+nff, fuu…！」</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -6216,8 +6226,8 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>I like stronger sensations too, but when she's licking
-me gently my emotions start to rise.</t>
+          <t>I like stronger sensations too, but when she's
+licking me gently my emotions start to rise.</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -6247,8 +6257,8 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t>「lero...reru！ fa, haa...jyuru！ hafu, lerolero...！ nfu,
-fu, jyururu！」</t>
+          <t>「lero...reru！ fa, haa...jyuru！ hafu, lerolero...！
+nfu, fu, jyururu！」</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -6401,8 +6411,8 @@
       </c>
       <c r="B386" s="1" t="inlineStr">
         <is>
-          <t>It feels like it's going to burst and it hurts, but it
-feels so good…！</t>
+          <t>It feels like it's going to burst and it hurts, but
+it feels so good…！</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -6432,8 +6442,8 @@
       </c>
       <c r="B388" s="1" t="inlineStr">
         <is>
-          <t>「Is that so？ But please hold on… amu… chu, chu！ chupu,
-rero…」</t>
+          <t>「Is that so？ But please hold on… amu… chu, chu！
+chupu, rero…」</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -6524,8 +6534,8 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t>「djupu, djupuppu！ hafu, ffu... afu, rero, rerorero！ n~
-chuu！ chuu！ chuu！」</t>
+          <t>「djupu, djupuppu！ hafu, ffu... afu, rero, rerorero！
+n~ chuu！ chuu！ chuu！」</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -6586,8 +6596,8 @@
       </c>
       <c r="B398" s="1" t="inlineStr">
         <is>
-          <t>「R-Ruri, Chiyo-chan... ah... if you do that so much, I
-can't hold back...！」</t>
+          <t>「R-Ruri, Chiyo-chan... ah... if you do that so much,
+I can't hold back...！」</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6664,8 +6674,8 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t>I thought it wasn’t like Rurichiyo-chan, but if it’s a
-punishment, it can’t be helped.</t>
+          <t>I thought it wasn’t like Rurichiyo-chan, but if it’s
+a punishment, it can’t be helped.</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -6982,8 +6992,8 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>Startled by the sudden movement, Rurichiyo-chan pulled
-her face away as if in reflex.</t>
+          <t>Startled by the sudden movement, Rurichiyo-chan
+pulled her face away as if in reflex.</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -7089,7 +7099,8 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t>I grit my teeth and endure the feeling of ejaculating.</t>
+          <t>I grit my teeth and endure the feeling of
+ejaculating.</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -7578,8 +7589,8 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>Even when I mess up, Rurichiyo-chan gently wraps me up
-and forgives me...</t>
+          <t>Even when I mess up, Rurichiyo-chan gently wraps me
+up and forgives me...</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -8135,8 +8146,8 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>Even though Rurichiyo-chan’s tongue hadn’t changed, my
-penis started twitching uncontrollably.</t>
+          <t>Even though Rurichiyo-chan’s tongue hadn’t changed,
+my penis started twitching uncontrollably.</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8272,9 +8283,9 @@
       </c>
       <c r="B508" s="1" t="inlineStr">
         <is>
-          <t>To every movement of Rurichiyo-chan's tongue, my penis
-overreacted, the stimulation traveling from my hips up
-to my chest.</t>
+          <t>To every movement of Rurichiyo-chan's tongue, my
+penis overreacted, the stimulation traveling from my
+hips up to my chest.</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -8977,8 +8988,8 @@
       </c>
       <c r="B554" s="1" t="inlineStr">
         <is>
-          <t>At that instant a sharp, stinging pain shot through me
-again...</t>
+          <t>At that instant a sharp, stinging pain shot through
+me again...</t>
         </is>
       </c>
       <c r="C554" t="n">

--- a/processed_ruby_restored_xlsx/sc224_瑠璃６：おしりペンペン.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc224_瑠璃６：おしりペンペン.ss.xlsx
@@ -942,8 +942,8 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Although I never skipped cleaning the dorm, at heart
-I was lazy, and I found cleaning my own room
+          <t>Although he never skipped cleaning the dorm, at heart
+he was lazy, and he found cleaning his own room
 bothersome.</t>
         </is>
       </c>
@@ -960,7 +960,7 @@
       <c r="B33" s="1" t="inlineStr">
         <is>
           <t>Seeing that, Rurichiyo-chan would sometimes clean it
-for me.</t>
+for him.</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Rurichiyo-chan</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1749,8 +1749,8 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>「Oji-sama, it's wrong for you to be holding a girl's
-panties, isn't it？」</t>
+          <t>Oji-sama, it's wrong for you to be holding a girl's
+panties, isn't it？</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>I got spanked on the butt and couldn't help but let
+          <t>He got spanked on the butt and couldn't help but let
 out a sound.</t>
         </is>
       </c>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>「Ooooh...！」</t>
+          <t>Ooooh...！</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>「…！」</t>
+          <t>…！</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -3317,8 +3317,8 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>If she's going out of her way to repeat it, does that
-mean she's that mad...?</t>
+          <t>If they're going out of their way to repeat it, does
+that mean they're that mad...?</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>「Th-tha-that's... what is that...?」</t>
+          <t>Th-tha-that's... what is that...?</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>Although my explanation was lacking, I read the air
+          <t>Although my explanation was lacking, he read the air
 and understood, and I ended up repeating 'penis' over
 and over in the heat of the moment.</t>
         </is>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>「Come now, Oji-sama. Please lie on your back.」</t>
+          <t>Come now, Oji-sama. Please lie on your back.</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>「Huh？ …like this...？」</t>
+          <t>Huh？ …like this...？</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>When I answered obediently and lay on my back, my
+          <t>When I answered obediently and lay on my back, his
 penis, defying gravity, pointed upward.</t>
         </is>
       </c>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>Rurichiyo</t>
+          <t>Ruri</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4498,7 +4498,7 @@
       <c r="B262" s="1" t="inlineStr">
         <is>
           <t>It sounds like she's sulking, and it also looks like
-she's trying to hide her embarrassment...</t>
+she's trying to hide her embarrassment..."</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>「W-what, are you laughing at me...?！」</t>
+          <t>「W-what, are you laughing at me...?！</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4791,8 +4791,8 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>「Puaa... Ah... I did something I shouldn't have
-again... That's not allowed, is it...？ Hey！」</t>
+          <t>Puaa... Ah... I did something I shouldn't have
+again... That's not allowed, is it...？ Hey！</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -5068,8 +5068,8 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>「Nnmm... kimohiyo shashoresu ne... jyuru, jyuru,
-jyuru...」</t>
+          <t>Nnmm... kimohiyo shashoresu ne... jyuru, jyuru,
+jyuru...</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nnh！？ Nmm... slurp, slurp！ Nnh...？ shlp, pff...」</t>
+          <t>Nn, nnh！？ Nmm... slurp, slurp！ Nnh...？ shlp, pff...</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="B310" s="1" t="inlineStr">
         <is>
-          <t>She tries to hold the sound in somehow but fails, and
+          <t>They try to hold the sound in somehow but fail, and
 the sucking sound only gets louder.</t>
         </is>
       </c>
@@ -5410,8 +5410,8 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>But the scolded son had no intention of reflecting; I
-cheerfully kept twitching and bouncing around.</t>
+          <t>But the scolded son had no intention of reflecting;
+he cheerfully kept twitching and bouncing around.</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>My charged-up penis wobbled around in
+          <t>His charged-up penis wobbled around in
 Rurichiyo-chan's hand.</t>
         </is>
       </c>
@@ -6132,9 +6132,9 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>Just when I thought she was angry, she smiled now as
-if soothing a small child, and then opened wide and
-took me in again...</t>
+          <t>Just when I thought they were angry, they smiled now
+as if soothing a small child, and then opened wide
+and took me in again...</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="B427" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh…！？ Hah, ah, aaah…！」</t>
+          <t>Nnngh…！？ Hah, ah, aaah…！</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="B434" s="1" t="inlineStr">
         <is>
-          <t>「Ugh… haah…！」</t>
+          <t>Ugh… haah…！</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="B447" s="1" t="inlineStr">
         <is>
-          <t>「Nn… kuu…」</t>
+          <t>Nn… kuu…</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="B475" s="1" t="inlineStr">
         <is>
-          <t>When I strained my penis, Rurichiyo-chan instantly
+          <t>When he strained his penis, Rurichiyo-chan instantly
 pouted and said.</t>
         </is>
       </c>
@@ -8147,7 +8147,7 @@
       <c r="B499" s="1" t="inlineStr">
         <is>
           <t>Even though Rurichiyo-chan’s tongue hadn’t changed,
-my penis started twitching uncontrollably.</t>
+his penis started twitching uncontrollably.</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8177,7 +8177,7 @@
       </c>
       <c r="B501" s="1" t="inlineStr">
         <is>
-          <t>「Nngh... ah, ah...」</t>
+          <t>Nngh... ah, ah...</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -8345,7 +8345,7 @@
       </c>
       <c r="B512" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nn！ Chu~...n！ Chup, chup！ Chuju, n~...」</t>
+          <t>Nn, nn！ Chu~...n！ Chup, chup！ Chuju, n~...</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>「Nn？ Nfu-fu！ Rero, rero... Nn~... nn！ nn！ nn！ nn！」</t>
+          <t>Nn？ Nfu-fu！ Rero, rero... Nn~... nn！ nn！ nn！ nn！</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>「Nngh！ Nngh！ Nngh！ Nmpf！ Hah, ngh！」</t>
+          <t>Nngh！ Nngh！ Nngh！ Nmpf！ Hah, ngh！</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="B526" s="1" t="inlineStr">
         <is>
-          <t>「A...! Ka—!」</t>
+          <t>A...! Ka—!</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="B534" s="1" t="inlineStr">
         <is>
-          <t>「Nnyaa...！？ Ah, aaah...」</t>
+          <t>Nnyaa...！？ Ah, aaah...</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="B536" s="1" t="inlineStr">
         <is>
-          <t>「Uwaaaaah！　Ah！　Aaaaaaah…！」</t>
+          <t>Uwaaaaah！　Ah！　Aaaaaaah…！</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="B546" s="1" t="inlineStr">
         <is>
-          <t>I probably never thought I'd suffer this much.</t>
+          <t>He probably never thought he'd suffer this much.</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="B557" s="1" t="inlineStr">
         <is>
-          <t>「Huff！　Huff！　Huff！　Huff！」</t>
+          <t>Huff！　Huff！　Huff！　Huff！</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -9081,8 +9081,8 @@
       </c>
       <c r="B560" s="1" t="inlineStr">
         <is>
-          <t>「Ah, um… I'm truly sorry. I think I went a bit too
-far…」</t>
+          <t>Ah, um… I」m truly sorry. I think I went a bit too
+far…</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="B574" s="1" t="inlineStr">
         <is>
-          <t>「B-b-but, b-b-but...」</t>
+          <t>B-b-but, b-b-but...</t>
         </is>
       </c>
       <c r="C574" t="n">
